--- a/food_beverage_order_forms/019_menu_order_form--food_beverage_order_forms.xlsx
+++ b/food_beverage_order_forms/019_menu_order_form--food_beverage_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -612,7 +612,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>payment_info</t>
+          <t>payment_info_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>payment total</t>
+          <t>payment total (2)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,7 +865,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>form_data</t>
+          <t>form_data_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>phone_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Phone 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>name_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>Name 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>address_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>Address 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>payment</t>
+          <t>payment_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>payment</t>
+          <t>Payment 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>payment_method</t>
+          <t>payment_method_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>payment method</t>
+          <t>Payment Method 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1078,9 +1078,9 @@
   <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1193,63 +1193,63 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>form_data_choices</t>
+          <t>form_data_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'option_4'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Option 4'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>form_data_choices</t>
+          <t>form_data_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'option_5'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Option 5'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>form_data_choices</t>
+          <t>form_data_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'option_6'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Option 6'}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -1261,12 +1261,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'option_7'}</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Option 7'}</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'option_8'}</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Option 8'}</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -1295,63 +1295,63 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'option_9'}</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Option 9'}</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_method_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'option_4'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Option 4'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_method_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'option_5'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Option 5'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_method_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'option_6'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Option 6'}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
